--- a/Testkit_Q1_PRN222/Q12/TC4/Header.xlsx
+++ b/Testkit_Q1_PRN222/Q12/TC4/Header.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27C2D32-1BA0-4882-B8BF-42031DEF8858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D225EBD9-2AEB-4BAF-83C1-1CE867A02DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -429,13 +429,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.21875" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="1" max="1" width="21.19921875" customWidth="1"/>
+    <col min="2" max="2" width="15.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -443,7 +443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -451,15 +451,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -467,7 +467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -475,7 +475,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
     </row>
   </sheetData>
@@ -486,9 +486,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE63C1B-9C74-4B75-BB3A-89FABA520B88}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
@@ -499,7 +499,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -508,7 +508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>12</v>

--- a/Testkit_Q1_PRN222/Q12/TC4/Header.xlsx
+++ b/Testkit_Q1_PRN222/Q12/TC4/Header.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D225EBD9-2AEB-4BAF-83C1-1CE867A02DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A856A5EF-22FE-4252-A633-4D9C6718F81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -71,12 +71,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Grade_Content</t>
-  </si>
-  <si>
-    <t>Server</t>
   </si>
 </sst>
 </file>
@@ -456,7 +450,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -468,12 +462,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>

--- a/Testkit_Q1_PRN222/Q12/TC4/Header.xlsx
+++ b/Testkit_Q1_PRN222/Q12/TC4/Header.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A856A5EF-22FE-4252-A633-4D9C6718F81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6634FEC-509B-4328-A0E0-F4CE468ACA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>Test Case ID</t>
   </si>
   <si>
-    <t>TC01</t>
-  </si>
-  <si>
     <t>Execution Date</t>
   </si>
   <si>
@@ -71,6 +68,9 @@
   </si>
   <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>TC1</t>
   </si>
 </sst>
 </file>
@@ -434,31 +434,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -479,31 +479,31 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
